--- a/Daily_Report/Top 7 broker List with its Turnover 2024-11-20.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-11-20.xlsx
@@ -101,67 +101,67 @@
     <t>49</t>
   </si>
   <si>
-    <t>977,326,178.78</t>
-  </si>
-  <si>
-    <t>602,788,641.4</t>
-  </si>
-  <si>
-    <t>514,706,230.2</t>
-  </si>
-  <si>
-    <t>472,192,063.4</t>
-  </si>
-  <si>
-    <t>436,538,972.7</t>
-  </si>
-  <si>
-    <t>424,886,595.95</t>
-  </si>
-  <si>
-    <t>419,319,457.0</t>
-  </si>
-  <si>
-    <t>522,184,695.38</t>
-  </si>
-  <si>
-    <t>309,887,108.7</t>
-  </si>
-  <si>
-    <t>269,965,430.3</t>
-  </si>
-  <si>
-    <t>233,740,063.4</t>
-  </si>
-  <si>
-    <t>206,125,374.2</t>
-  </si>
-  <si>
-    <t>185,461,559.3</t>
-  </si>
-  <si>
-    <t>191,546,520.2</t>
-  </si>
-  <si>
-    <t>455,141,483.4</t>
-  </si>
-  <si>
-    <t>292,901,532.7</t>
-  </si>
-  <si>
-    <t>244,740,799.9</t>
-  </si>
-  <si>
-    <t>238,452,000.0</t>
-  </si>
-  <si>
-    <t>230,413,598.5</t>
-  </si>
-  <si>
-    <t>239,425,036.65</t>
-  </si>
-  <si>
-    <t>227,772,936.8</t>
+    <t>979,868,445.38</t>
+  </si>
+  <si>
+    <t>603,788,442.9</t>
+  </si>
+  <si>
+    <t>513,656,078.2</t>
+  </si>
+  <si>
+    <t>470,680,118.4</t>
+  </si>
+  <si>
+    <t>436,400,960.5</t>
+  </si>
+  <si>
+    <t>426,497,083.75</t>
+  </si>
+  <si>
+    <t>418,885,997.5</t>
+  </si>
+  <si>
+    <t>524,418,497.38</t>
+  </si>
+  <si>
+    <t>310,765,182.39</t>
+  </si>
+  <si>
+    <t>268,949,948.3</t>
+  </si>
+  <si>
+    <t>232,932,599.9</t>
+  </si>
+  <si>
+    <t>206,252,937.4</t>
+  </si>
+  <si>
+    <t>186,115,364.9</t>
+  </si>
+  <si>
+    <t>191,370,103.6</t>
+  </si>
+  <si>
+    <t>455,449,948.0</t>
+  </si>
+  <si>
+    <t>293,023,260.5</t>
+  </si>
+  <si>
+    <t>244,706,129.9</t>
+  </si>
+  <si>
+    <t>237,747,518.5</t>
+  </si>
+  <si>
+    <t>230,148,023.1</t>
+  </si>
+  <si>
+    <t>240,381,718.85</t>
+  </si>
+  <si>
+    <t>227,515,893.9</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -182,7 +182,7 @@
     <t>NGPL</t>
   </si>
   <si>
-    <t>100,666,775.4</t>
+    <t>100,560,307.8</t>
   </si>
   <si>
     <t>JFL</t>
@@ -212,16 +212,16 @@
     <t>NFS</t>
   </si>
   <si>
-    <t>108,921,836.5</t>
-  </si>
-  <si>
-    <t>106,069,111.1</t>
+    <t>109,651,336.5</t>
+  </si>
+  <si>
+    <t>105,691,201.1</t>
   </si>
   <si>
     <t>SHEL</t>
   </si>
   <si>
-    <t>4,453,064.8</t>
+    <t>4,507,864.8</t>
   </si>
   <si>
     <t>2,972,629.1</t>
@@ -230,7 +230,7 @@
     <t>BFC</t>
   </si>
   <si>
-    <t>2,746,487.0</t>
+    <t>2,712,242.0</t>
   </si>
   <si>
     <t>SCB</t>
@@ -269,31 +269,31 @@
     <t>8,910,531.0</t>
   </si>
   <si>
+    <t>7,264,946.0</t>
+  </si>
+  <si>
     <t>CGH</t>
   </si>
   <si>
     <t>7,228,765.5</t>
   </si>
   <si>
-    <t>7,216,446.0</t>
-  </si>
-  <si>
     <t>MDB</t>
   </si>
   <si>
-    <t>5,347,320.0</t>
+    <t>5,212,520.0</t>
   </si>
   <si>
     <t>CLI</t>
   </si>
   <si>
-    <t>13,225,559.0</t>
+    <t>13,157,360.0</t>
   </si>
   <si>
     <t>8,025,977.2</t>
   </si>
   <si>
-    <t>5,132,784.5</t>
+    <t>5,247,492.5</t>
   </si>
   <si>
     <t>PROFL</t>
@@ -320,16 +320,16 @@
     <t>5,450,239.0</t>
   </si>
   <si>
+    <t>5,377,174.6</t>
+  </si>
+  <si>
     <t>5,256,570.59</t>
   </si>
   <si>
-    <t>5,224,774.59</t>
-  </si>
-  <si>
-    <t>7,171,442.0</t>
-  </si>
-  <si>
-    <t>6,270,651.3</t>
+    <t>7,200,624.0</t>
+  </si>
+  <si>
+    <t>6,173,651.3</t>
   </si>
   <si>
     <t>UHEWA</t>
@@ -341,7 +341,7 @@
     <t>4,272,529.8</t>
   </si>
   <si>
-    <t>4,006,184.2</t>
+    <t>4,009,979.2</t>
   </si>
   <si>
     <t>Sell Amount</t>
@@ -350,10 +350,10 @@
     <t>130,050,250.6</t>
   </si>
   <si>
-    <t>15,358,734.6</t>
-  </si>
-  <si>
-    <t>13,838,411.5</t>
+    <t>15,424,774.6</t>
+  </si>
+  <si>
+    <t>13,853,002.5</t>
   </si>
   <si>
     <t>11,664,090.5</t>
@@ -365,7 +365,7 @@
     <t>9,582,449.3</t>
   </si>
   <si>
-    <t>122,619,048.0</t>
+    <t>122,745,148.0</t>
   </si>
   <si>
     <t>57,445,302.5</t>
@@ -398,7 +398,13 @@
     <t>7,644,631.5</t>
   </si>
   <si>
-    <t>16,734,874.7</t>
+    <t>16,531,434.7</t>
+  </si>
+  <si>
+    <t>ICFC</t>
+  </si>
+  <si>
+    <t>8,824,752.19</t>
   </si>
   <si>
     <t>8,553,071.69</t>
@@ -410,12 +416,6 @@
     <t>8,495,710.0</t>
   </si>
   <si>
-    <t>ICFC</t>
-  </si>
-  <si>
-    <t>8,360,440.5</t>
-  </si>
-  <si>
     <t>MMKJL</t>
   </si>
   <si>
@@ -431,7 +431,7 @@
     <t>10,482,717.0</t>
   </si>
   <si>
-    <t>7,055,007.4</t>
+    <t>7,276,277.4</t>
   </si>
   <si>
     <t>SWMFPO</t>
@@ -440,16 +440,16 @@
     <t>6,826,906.8</t>
   </si>
   <si>
-    <t>6,350,590.6</t>
+    <t>6,266,075.6</t>
   </si>
   <si>
     <t>18,800,412.0</t>
   </si>
   <si>
-    <t>10,779,489.1</t>
-  </si>
-  <si>
-    <t>9,845,999.4</t>
+    <t>11,285,822.3</t>
+  </si>
+  <si>
+    <t>9,983,372.5</t>
   </si>
   <si>
     <t>6,591,605.7</t>
@@ -464,13 +464,13 @@
     <t>13,250,728.8</t>
   </si>
   <si>
-    <t>8,425,384.6</t>
-  </si>
-  <si>
-    <t>6,928,444.4</t>
-  </si>
-  <si>
-    <t>6,337,405.9</t>
+    <t>8,552,634.6</t>
+  </si>
+  <si>
+    <t>7,001,234.4</t>
+  </si>
+  <si>
+    <t>6,328,955.9</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -488,103 +488,103 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>329,494,259.89</t>
-  </si>
-  <si>
-    <t>322,846,073.1</t>
-  </si>
-  <si>
-    <t>231,889,757.9</t>
-  </si>
-  <si>
-    <t>190,948,357.9</t>
-  </si>
-  <si>
-    <t>154,871,315.0</t>
+    <t>328,190,259.89</t>
+  </si>
+  <si>
+    <t>322,051,558.1</t>
+  </si>
+  <si>
+    <t>232,273,312.3</t>
+  </si>
+  <si>
+    <t>191,793,630.9</t>
+  </si>
+  <si>
+    <t>155,147,667.0</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>2,026,226,939.8</t>
+    <t>2,023,060,446.6</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>1,352,602,450.7</t>
+    <t>1,353,073,437.09</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>1,322,593,940.84</t>
+    <t>1,322,280,766.75</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>983,025,438.3</t>
+    <t>982,836,860.3</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>398,854,146.5</t>
+    <t>397,032,304.3</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>374,393,053.01</t>
+    <t>373,370,010.81</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>212,780,188.8</t>
+    <t>213,997,187.5</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>106,259,759.4</t>
+    <t>106,653,115.9</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>97,789,772.9</t>
+    <t>98,006,112.9</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>84,030,240.8</t>
+    <t>83,907,250.8</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>69,470,115.09</t>
+    <t>69,457,304.4</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>38,069,797.0</t>
+    <t>38,132,317.0</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>20,081,408.43</t>
+    <t>20,094,832.43</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>7,719,998.6</t>
+    <t>8,705,887.6</t>
   </si>
   <si>
     <t>Tradings</t>
@@ -602,88 +602,88 @@
     <t>100%</t>
   </si>
   <si>
-    <t>223,488,607.5</t>
-  </si>
-  <si>
-    <t>75,105,908.09</t>
-  </si>
-  <si>
-    <t>57,673,435.8</t>
-  </si>
-  <si>
-    <t>52,881,968.7</t>
-  </si>
-  <si>
-    <t>50,520,815.3</t>
-  </si>
-  <si>
-    <t>232,416,903.5</t>
-  </si>
-  <si>
-    <t>28,593,127.5</t>
-  </si>
-  <si>
-    <t>19,640,300.2</t>
+    <t>224,700,869.5</t>
+  </si>
+  <si>
+    <t>75,014,478.59</t>
+  </si>
+  <si>
+    <t>57,457,959.8</t>
+  </si>
+  <si>
+    <t>52,912,570.7</t>
+  </si>
+  <si>
+    <t>51,761,645.3</t>
+  </si>
+  <si>
+    <t>233,136,248.5</t>
+  </si>
+  <si>
+    <t>28,579,971.5</t>
+  </si>
+  <si>
+    <t>20,010,549.39</t>
   </si>
   <si>
     <t>7,694,116.6</t>
   </si>
   <si>
-    <t>6,228,923.9</t>
-  </si>
-  <si>
-    <t>65,437,593.3</t>
-  </si>
-  <si>
-    <t>65,392,379.7</t>
-  </si>
-  <si>
-    <t>40,476,872.5</t>
-  </si>
-  <si>
-    <t>32,783,345.2</t>
+    <t>5,940,229.9</t>
+  </si>
+  <si>
+    <t>65,549,229.3</t>
+  </si>
+  <si>
+    <t>64,636,379.7</t>
+  </si>
+  <si>
+    <t>40,246,258.5</t>
+  </si>
+  <si>
+    <t>32,742,511.2</t>
   </si>
   <si>
     <t>19,509,871.8</t>
   </si>
   <si>
-    <t>77,379,909.9</t>
-  </si>
-  <si>
-    <t>48,657,896.0</t>
-  </si>
-  <si>
-    <t>42,574,908.29</t>
-  </si>
-  <si>
-    <t>15,400,945.0</t>
-  </si>
-  <si>
-    <t>9,778,065.8</t>
-  </si>
-  <si>
-    <t>62,484,512.1</t>
-  </si>
-  <si>
-    <t>56,019,679.2</t>
-  </si>
-  <si>
-    <t>28,533,531.6</t>
-  </si>
-  <si>
-    <t>13,828,604.7</t>
+    <t>77,149,627.9</t>
+  </si>
+  <si>
+    <t>48,811,372.0</t>
+  </si>
+  <si>
+    <t>42,225,750.79</t>
+  </si>
+  <si>
+    <t>15,360,185.0</t>
+  </si>
+  <si>
+    <t>9,437,325.8</t>
+  </si>
+  <si>
+    <t>62,553,388.1</t>
+  </si>
+  <si>
+    <t>55,945,885.4</t>
+  </si>
+  <si>
+    <t>28,672,481.6</t>
+  </si>
+  <si>
+    <t>13,869,449.7</t>
   </si>
   <si>
     <t>13,751,548.1</t>
   </si>
   <si>
-    <t>62,862,787.3</t>
-  </si>
-  <si>
-    <t>39,058,441.6</t>
-  </si>
-  <si>
-    <t>31,016,589.5</t>
+    <t>62,655,927.3</t>
+  </si>
+  <si>
+    <t>39,862,621.2</t>
+  </si>
+  <si>
+    <t>31,123,155.5</t>
   </si>
   <si>
     <t>18,885,474.3</t>
@@ -692,43 +692,43 @@
     <t>12,793,979.5</t>
   </si>
   <si>
-    <t>64,156,226.4</t>
-  </si>
-  <si>
-    <t>37,268,508.79</t>
-  </si>
-  <si>
-    <t>33,219,771.0</t>
-  </si>
-  <si>
-    <t>18,712,762.0</t>
-  </si>
-  <si>
-    <t>11,695,464.0</t>
-  </si>
-  <si>
-    <t>225,454,280.8</t>
-  </si>
-  <si>
-    <t>77,149,842.4</t>
-  </si>
-  <si>
-    <t>52,581,435.0</t>
+    <t>64,186,122.2</t>
+  </si>
+  <si>
+    <t>37,223,990.79</t>
+  </si>
+  <si>
+    <t>33,171,165.6</t>
+  </si>
+  <si>
+    <t>18,627,442.0</t>
+  </si>
+  <si>
+    <t>11,712,195.0</t>
+  </si>
+  <si>
+    <t>225,380,922.8</t>
+  </si>
+  <si>
+    <t>77,748,041.9</t>
+  </si>
+  <si>
+    <t>52,576,070.6</t>
   </si>
   <si>
     <t>42,717,596.6</t>
   </si>
   <si>
-    <t>24,626,431.0</t>
-  </si>
-  <si>
-    <t>201,921,055.9</t>
-  </si>
-  <si>
-    <t>31,027,856.6</t>
-  </si>
-  <si>
-    <t>23,242,897.6</t>
+    <t>24,469,376.5</t>
+  </si>
+  <si>
+    <t>202,047,155.9</t>
+  </si>
+  <si>
+    <t>30,981,555.4</t>
+  </si>
+  <si>
+    <t>23,023,837.6</t>
   </si>
   <si>
     <t>16,291,084.1</t>
@@ -737,73 +737,73 @@
     <t>5,089,865.5</t>
   </si>
   <si>
-    <t>68,440,295.09</t>
-  </si>
-  <si>
-    <t>46,637,323.6</t>
-  </si>
-  <si>
-    <t>43,991,172.8</t>
-  </si>
-  <si>
-    <t>28,550,279.9</t>
-  </si>
-  <si>
-    <t>16,912,508.1</t>
-  </si>
-  <si>
-    <t>69,121,180.3</t>
-  </si>
-  <si>
-    <t>46,345,164.1</t>
-  </si>
-  <si>
-    <t>41,702,238.2</t>
-  </si>
-  <si>
-    <t>24,423,328.8</t>
-  </si>
-  <si>
-    <t>21,721,592.2</t>
-  </si>
-  <si>
-    <t>69,423,596.09</t>
-  </si>
-  <si>
-    <t>54,441,745.1</t>
-  </si>
-  <si>
-    <t>40,152,964.5</t>
-  </si>
-  <si>
-    <t>31,150,672.4</t>
-  </si>
-  <si>
-    <t>11,138,690.1</t>
-  </si>
-  <si>
-    <t>75,088,492.59</t>
-  </si>
-  <si>
-    <t>62,721,113.2</t>
-  </si>
-  <si>
-    <t>41,543,923.29</t>
-  </si>
-  <si>
-    <t>23,733,832.4</t>
-  </si>
-  <si>
-    <t>13,390,715.9</t>
-  </si>
-  <si>
-    <t>60,393,033.0</t>
-  </si>
-  <si>
-    <t>55,279,514.8</t>
-  </si>
-  <si>
-    <t>43,342,548.7</t>
+    <t>68,577,525.09</t>
+  </si>
+  <si>
+    <t>46,464,621.1</t>
+  </si>
+  <si>
+    <t>44,807,342.8</t>
+  </si>
+  <si>
+    <t>28,793,279.9</t>
+  </si>
+  <si>
+    <t>16,101,664.1</t>
+  </si>
+  <si>
+    <t>68,415,268.3</t>
+  </si>
+  <si>
+    <t>46,838,959.8</t>
+  </si>
+  <si>
+    <t>41,350,811.7</t>
+  </si>
+  <si>
+    <t>24,425,478.8</t>
+  </si>
+  <si>
+    <t>21,589,192.2</t>
+  </si>
+  <si>
+    <t>69,135,286.09</t>
+  </si>
+  <si>
+    <t>54,514,783.3</t>
+  </si>
+  <si>
+    <t>39,666,384.9</t>
+  </si>
+  <si>
+    <t>31,417,312.4</t>
+  </si>
+  <si>
+    <t>11,342,673.1</t>
+  </si>
+  <si>
+    <t>75,163,446.7</t>
+  </si>
+  <si>
+    <t>63,633,347.3</t>
+  </si>
+  <si>
+    <t>41,506,504.29</t>
+  </si>
+  <si>
+    <t>23,895,832.4</t>
+  </si>
+  <si>
+    <t>13,345,071.9</t>
+  </si>
+  <si>
+    <t>60,039,805.5</t>
+  </si>
+  <si>
+    <t>55,467,059.8</t>
+  </si>
+  <si>
+    <t>43,102,041.3</t>
   </si>
   <si>
     <t>20,835,750.0</t>
@@ -1618,7 +1618,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1030022295378015</v>
+        <v>0.1026263354781284</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1627,7 +1627,7 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1806965642999258</v>
+        <v>0.1816055570281271</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>72</v>
@@ -1636,7 +1636,7 @@
         <v>73</v>
       </c>
       <c r="J9" s="14">
-        <v>0.05919492501219776</v>
+        <v>0.0593159469790929</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>54</v>
@@ -1645,7 +1645,7 @@
         <v>81</v>
       </c>
       <c r="M9" s="16">
-        <v>0.07621227883602756</v>
+        <v>0.07645709218042043</v>
       </c>
       <c r="N9" s="17" t="s">
         <v>89</v>
@@ -1654,7 +1654,7 @@
         <v>90</v>
       </c>
       <c r="P9" s="18">
-        <v>0.03029639923830792</v>
+        <v>0.0301497044940624</v>
       </c>
       <c r="Q9" s="15" t="s">
         <v>62</v>
@@ -1663,7 +1663,7 @@
         <v>97</v>
       </c>
       <c r="S9" s="16">
-        <v>0.0234446035599867</v>
+        <v>0.02335607482333694</v>
       </c>
       <c r="T9" s="17" t="s">
         <v>64</v>
@@ -1672,7 +1672,7 @@
         <v>103</v>
       </c>
       <c r="V9" s="18">
-        <v>0.01710257389749505</v>
+        <v>0.0171899372215229</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1684,7 +1684,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.03811707657979942</v>
+        <v>0.03801818190558538</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>56</v>
@@ -1693,7 +1693,7 @@
         <v>66</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1759640175927177</v>
+        <v>0.1750467441747716</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>74</v>
@@ -1702,7 +1702,7 @@
         <v>75</v>
       </c>
       <c r="J10" s="14">
-        <v>0.03320254039543973</v>
+        <v>0.03327042183533924</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>82</v>
@@ -1711,7 +1711,7 @@
         <v>83</v>
       </c>
       <c r="M10" s="16">
-        <v>0.01887056494732266</v>
+        <v>0.01893118203141848</v>
       </c>
       <c r="N10" s="17" t="s">
         <v>62</v>
@@ -1720,7 +1720,7 @@
         <v>91</v>
       </c>
       <c r="P10" s="18">
-        <v>0.01838547690337752</v>
+        <v>0.0183912913271418</v>
       </c>
       <c r="Q10" s="15" t="s">
         <v>54</v>
@@ -1729,7 +1729,7 @@
         <v>98</v>
       </c>
       <c r="S10" s="16">
-        <v>0.01449917827185341</v>
+        <v>0.01444442819123965</v>
       </c>
       <c r="T10" s="17" t="s">
         <v>56</v>
@@ -1738,7 +1738,7 @@
         <v>104</v>
       </c>
       <c r="V10" s="18">
-        <v>0.01495435328678297</v>
+        <v>0.01473826133326407</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1750,7 +1750,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.02597338877352854</v>
+        <v>0.025906000871531</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>67</v>
@@ -1759,7 +1759,7 @@
         <v>68</v>
       </c>
       <c r="G11" s="12">
-        <v>0.007387439799226449</v>
+        <v>0.007465967348345879</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>76</v>
@@ -1768,16 +1768,16 @@
         <v>77</v>
       </c>
       <c r="J11" s="14">
-        <v>0.02104637434792799</v>
+        <v>0.0210894029288253</v>
       </c>
       <c r="K11" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="L11" s="15" t="s">
-        <v>85</v>
-      </c>
       <c r="M11" s="16">
-        <v>0.01530895171754808</v>
+        <v>0.01543499654222914</v>
       </c>
       <c r="N11" s="17" t="s">
         <v>54</v>
@@ -1786,7 +1786,7 @@
         <v>92</v>
       </c>
       <c r="P11" s="18">
-        <v>0.01175790667269328</v>
+        <v>0.0120244751386151</v>
       </c>
       <c r="Q11" s="15" t="s">
         <v>99</v>
@@ -1795,7 +1795,7 @@
         <v>100</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01282751456965561</v>
+        <v>0.01277907682762673</v>
       </c>
       <c r="T11" s="17" t="s">
         <v>105</v>
@@ -1804,7 +1804,7 @@
         <v>106</v>
       </c>
       <c r="V11" s="18">
-        <v>0.01460282678940892</v>
+        <v>0.01461793766453127</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1816,7 +1816,7 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.02069312931456069</v>
+        <v>0.02063944103451256</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>62</v>
@@ -1825,7 +1825,7 @@
         <v>69</v>
       </c>
       <c r="G12" s="12">
-        <v>0.00493146170288802</v>
+        <v>0.00492329579168896</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>78</v>
@@ -1834,16 +1834,16 @@
         <v>79</v>
       </c>
       <c r="J12" s="14">
-        <v>0.01376918440883485</v>
+        <v>0.01379733502781706</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="L12" s="15" t="s">
         <v>86</v>
       </c>
       <c r="M12" s="16">
-        <v>0.01528286169834849</v>
+        <v>0.01535812798843725</v>
       </c>
       <c r="N12" s="17" t="s">
         <v>93</v>
@@ -1852,16 +1852,16 @@
         <v>94</v>
       </c>
       <c r="P12" s="18">
-        <v>0.00957302042049727</v>
+        <v>0.00957604789689733</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="R12" s="15" t="s">
         <v>101</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01237170259100992</v>
+        <v>0.01260776405015688</v>
       </c>
       <c r="T12" s="17" t="s">
         <v>87</v>
@@ -1870,7 +1870,7 @@
         <v>107</v>
       </c>
       <c r="V12" s="18">
-        <v>0.01018919997313647</v>
+        <v>0.01019974366653304</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1882,7 +1882,7 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01672952454871312</v>
+        <v>0.01668611983281008</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>70</v>
@@ -1891,7 +1891,7 @@
         <v>71</v>
       </c>
       <c r="G13" s="12">
-        <v>0.004556301846732177</v>
+        <v>0.004492040269888379</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>54</v>
@@ -1900,7 +1900,7 @@
         <v>80</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01375727645116816</v>
+        <v>0.01378540272474478</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>87</v>
@@ -1909,7 +1909,7 @@
         <v>88</v>
       </c>
       <c r="M13" s="16">
-        <v>0.0113244597156014</v>
+        <v>0.01107444269734424</v>
       </c>
       <c r="N13" s="17" t="s">
         <v>95</v>
@@ -1918,16 +1918,16 @@
         <v>96</v>
       </c>
       <c r="P13" s="18">
-        <v>0.009208211067932447</v>
+        <v>0.00921112317304352</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="R13" s="15" t="s">
         <v>102</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01229686850515483</v>
+        <v>0.01232498603221692</v>
       </c>
       <c r="T13" s="17" t="s">
         <v>62</v>
@@ -1936,7 +1936,7 @@
         <v>108</v>
       </c>
       <c r="V13" s="18">
-        <v>0.00955401456603527</v>
+        <v>0.009572960719461624</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2016,7 +2016,7 @@
         <v>110</v>
       </c>
       <c r="D16" s="10">
-        <v>0.1330673969690879</v>
+        <v>0.1327221538903272</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>56</v>
@@ -2025,7 +2025,7 @@
         <v>116</v>
       </c>
       <c r="G16" s="12">
-        <v>0.2034196392871845</v>
+        <v>0.203291648661664</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>62</v>
@@ -2034,7 +2034,7 @@
         <v>121</v>
       </c>
       <c r="J16" s="14">
-        <v>0.02336662487129148</v>
+        <v>0.02341439712374458</v>
       </c>
       <c r="K16" s="15" t="s">
         <v>62</v>
@@ -2043,7 +2043,7 @@
         <v>127</v>
       </c>
       <c r="M16" s="16">
-        <v>0.0354408216425774</v>
+        <v>0.03512244102469402</v>
       </c>
       <c r="N16" s="17" t="s">
         <v>135</v>
@@ -2052,7 +2052,7 @@
         <v>136</v>
       </c>
       <c r="P16" s="18">
-        <v>0.024534085316044</v>
+        <v>0.02454184424280157</v>
       </c>
       <c r="Q16" s="15" t="s">
         <v>56</v>
@@ -2061,7 +2061,7 @@
         <v>142</v>
       </c>
       <c r="S16" s="16">
-        <v>0.04424807037737759</v>
+        <v>0.04408098605199431</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>56</v>
@@ -2070,7 +2070,7 @@
         <v>147</v>
       </c>
       <c r="V16" s="18">
-        <v>0.03606538725437679</v>
+        <v>0.0361027073959425</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2082,7 +2082,7 @@
         <v>111</v>
       </c>
       <c r="D17" s="10">
-        <v>0.01571505494631523</v>
+        <v>0.01574167907204948</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>64</v>
@@ -2091,7 +2091,7 @@
         <v>117</v>
       </c>
       <c r="G17" s="12">
-        <v>0.09529924513272357</v>
+        <v>0.09514144097242044</v>
       </c>
       <c r="H17" s="13" t="s">
         <v>70</v>
@@ -2100,16 +2100,16 @@
         <v>122</v>
       </c>
       <c r="J17" s="14">
-        <v>0.01970506709440643</v>
+        <v>0.01974535341924043</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M17" s="16">
-        <v>0.01811354396432238</v>
+        <v>0.01874893766492262</v>
       </c>
       <c r="N17" s="17" t="s">
         <v>54</v>
@@ -2118,7 +2118,7 @@
         <v>137</v>
       </c>
       <c r="P17" s="18">
-        <v>0.02401324430477362</v>
+        <v>0.02402083851508846</v>
       </c>
       <c r="Q17" s="15" t="s">
         <v>62</v>
@@ -2127,7 +2127,7 @@
         <v>143</v>
       </c>
       <c r="S17" s="16">
-        <v>0.02537027339235835</v>
+        <v>0.02646166346735308</v>
       </c>
       <c r="T17" s="17" t="s">
         <v>64</v>
@@ -2136,7 +2136,7 @@
         <v>148</v>
       </c>
       <c r="V17" s="18">
-        <v>0.03160055794882898</v>
+        <v>0.03163325792478895</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -2148,7 +2148,7 @@
         <v>112</v>
       </c>
       <c r="D18" s="10">
-        <v>0.01415946057771065</v>
+        <v>0.01413761466175973</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>70</v>
@@ -2157,7 +2157,7 @@
         <v>118</v>
       </c>
       <c r="G18" s="12">
-        <v>0.01508450487534353</v>
+        <v>0.01505952673808623</v>
       </c>
       <c r="H18" s="13" t="s">
         <v>74</v>
@@ -2166,16 +2166,16 @@
         <v>123</v>
       </c>
       <c r="J18" s="14">
-        <v>0.01779242850128609</v>
+        <v>0.01782880450298933</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="L18" s="15" t="s">
         <v>130</v>
       </c>
       <c r="M18" s="16">
-        <v>0.01799206437064397</v>
+        <v>0.01817172930327877</v>
       </c>
       <c r="N18" s="17" t="s">
         <v>70</v>
@@ -2184,7 +2184,7 @@
         <v>138</v>
       </c>
       <c r="P18" s="18">
-        <v>0.0161612315078415</v>
+        <v>0.01667337622644852</v>
       </c>
       <c r="Q18" s="15" t="s">
         <v>93</v>
@@ -2193,7 +2193,7 @@
         <v>144</v>
       </c>
       <c r="S18" s="16">
-        <v>0.02317324079848982</v>
+        <v>0.02340783297325418</v>
       </c>
       <c r="T18" s="17" t="s">
         <v>62</v>
@@ -2202,7 +2202,7 @@
         <v>149</v>
       </c>
       <c r="V18" s="18">
-        <v>0.02009299702016928</v>
+        <v>0.02041757101226569</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -2214,7 +2214,7 @@
         <v>113</v>
       </c>
       <c r="D19" s="10">
-        <v>0.01193469565561042</v>
+        <v>0.01190373111308486</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>62</v>
@@ -2223,7 +2223,7 @@
         <v>119</v>
       </c>
       <c r="G19" s="12">
-        <v>0.01225785124756002</v>
+        <v>0.01223755371088439</v>
       </c>
       <c r="H19" s="13" t="s">
         <v>56</v>
@@ -2232,7 +2232,7 @@
         <v>124</v>
       </c>
       <c r="J19" s="14">
-        <v>0.0174529614621323</v>
+        <v>0.01748864343527201</v>
       </c>
       <c r="K19" s="15" t="s">
         <v>131</v>
@@ -2241,7 +2241,7 @@
         <v>132</v>
       </c>
       <c r="M19" s="16">
-        <v>0.01770559301611506</v>
+        <v>0.01804985948605557</v>
       </c>
       <c r="N19" s="17" t="s">
         <v>139</v>
@@ -2250,7 +2250,7 @@
         <v>140</v>
       </c>
       <c r="P19" s="18">
-        <v>0.0156387109214453</v>
+        <v>0.01564365667797379</v>
       </c>
       <c r="Q19" s="15" t="s">
         <v>70</v>
@@ -2259,7 +2259,7 @@
         <v>145</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01551380006531364</v>
+        <v>0.0154552186899918</v>
       </c>
       <c r="T19" s="17" t="s">
         <v>93</v>
@@ -2268,7 +2268,7 @@
         <v>150</v>
       </c>
       <c r="V19" s="18">
-        <v>0.01652306918827285</v>
+        <v>0.01671393754335271</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -2280,7 +2280,7 @@
         <v>115</v>
       </c>
       <c r="D20" s="10">
-        <v>0.009804760691012911</v>
+        <v>0.00977932226022837</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>87</v>
@@ -2289,7 +2289,7 @@
         <v>120</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01006220851460125</v>
+        <v>0.01004554669988037</v>
       </c>
       <c r="H20" s="13" t="s">
         <v>125</v>
@@ -2298,7 +2298,7 @@
         <v>126</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01485241687676777</v>
+        <v>0.01488278212688343</v>
       </c>
       <c r="K20" s="15" t="s">
         <v>133</v>
@@ -2307,7 +2307,7 @@
         <v>134</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01740846476921111</v>
+        <v>0.01746438521334408</v>
       </c>
       <c r="N20" s="17" t="s">
         <v>99</v>
@@ -2316,7 +2316,7 @@
         <v>141</v>
       </c>
       <c r="P20" s="18">
-        <v>0.0145475913885111</v>
+        <v>0.01435852843408212</v>
       </c>
       <c r="Q20" s="15" t="s">
         <v>54</v>
@@ -2325,7 +2325,7 @@
         <v>146</v>
       </c>
       <c r="S20" s="16">
-        <v>0.010600435605481</v>
+        <v>0.01056040749540061</v>
       </c>
       <c r="T20" s="17" t="s">
         <v>99</v>
@@ -2334,7 +2334,7 @@
         <v>151</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01511355076470969</v>
+        <v>0.01510901757941909</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2404,7 +2404,7 @@
         <v>163</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2856705534444116</v>
+        <v>0.2852241207930862</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -2415,7 +2415,7 @@
         <v>165</v>
       </c>
       <c r="D32" s="22">
-        <v>0.1906986246663349</v>
+        <v>0.1907650273692651</v>
       </c>
     </row>
     <row r="33" spans="2:4">
@@ -2426,7 +2426,7 @@
         <v>167</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1864678312401366</v>
+        <v>0.1864236779339525</v>
       </c>
     </row>
     <row r="34" spans="2:4">
@@ -2437,7 +2437,7 @@
         <v>169</v>
       </c>
       <c r="D34" s="22">
-        <v>0.1385932718063728</v>
+        <v>0.1385666848626453</v>
       </c>
     </row>
     <row r="35" spans="2:4">
@@ -2448,7 +2448,7 @@
         <v>171</v>
       </c>
       <c r="D35" s="22">
-        <v>0.05623303221183114</v>
+        <v>0.05597617713832503</v>
       </c>
     </row>
     <row r="36" spans="2:4">
@@ -2459,7 +2459,7 @@
         <v>173</v>
       </c>
       <c r="D36" s="22">
-        <v>0.05278434935312157</v>
+        <v>0.05264011425993905</v>
       </c>
     </row>
     <row r="37" spans="2:4">
@@ -2470,7 +2470,7 @@
         <v>175</v>
       </c>
       <c r="D37" s="22">
-        <v>0.02999912453167868</v>
+        <v>0.0301707048642373</v>
       </c>
     </row>
     <row r="38" spans="2:4">
@@ -2481,7 +2481,7 @@
         <v>177</v>
       </c>
       <c r="D38" s="22">
-        <v>0.01498118679621556</v>
+        <v>0.01503664473473603</v>
       </c>
     </row>
     <row r="39" spans="2:4">
@@ -2492,7 +2492,7 @@
         <v>179</v>
       </c>
       <c r="D39" s="22">
-        <v>0.01378703342494485</v>
+        <v>0.0138175344346384</v>
       </c>
     </row>
     <row r="40" spans="2:4">
@@ -2503,7 +2503,7 @@
         <v>181</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01184712577050851</v>
+        <v>0.01182978584639735</v>
       </c>
     </row>
     <row r="41" spans="2:4">
@@ -2514,7 +2514,7 @@
         <v>183</v>
       </c>
       <c r="D41" s="22">
-        <v>0.009794345262442737</v>
+        <v>0.009792539127262554</v>
       </c>
     </row>
     <row r="42" spans="2:4">
@@ -2525,7 +2525,7 @@
         <v>185</v>
       </c>
       <c r="D42" s="22">
-        <v>0.005367325724916019</v>
+        <v>0.005376140198088065</v>
       </c>
     </row>
     <row r="43" spans="2:4">
@@ -2536,7 +2536,7 @@
         <v>187</v>
       </c>
       <c r="D43" s="22">
-        <v>0.002831206587702172</v>
+        <v>0.002833099189875262</v>
       </c>
     </row>
     <row r="44" spans="2:4">
@@ -2547,7 +2547,7 @@
         <v>189</v>
       </c>
       <c r="D44" s="22">
-        <v>0.001088415235891477</v>
+        <v>0.001227412231110856</v>
       </c>
     </row>
     <row r="45" spans="2:4">
@@ -2954,7 +2954,7 @@
         <v>195</v>
       </c>
       <c r="D9" s="10">
-        <v>0.2286735097784669</v>
+        <v>0.2293173849606509</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>164</v>
@@ -2963,7 +2963,7 @@
         <v>200</v>
       </c>
       <c r="G9" s="12">
-        <v>0.3855694808054159</v>
+        <v>0.3861224096642941</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>162</v>
@@ -2972,7 +2972,7 @@
         <v>205</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1271358096337261</v>
+        <v>0.127613070460888</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>162</v>
@@ -2981,7 +2981,7 @@
         <v>210</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1638738045337507</v>
+        <v>0.1639109554111985</v>
       </c>
       <c r="N9" s="17" t="s">
         <v>162</v>
@@ -2990,7 +2990,7 @@
         <v>215</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1431361596732873</v>
+        <v>0.1433392539474028</v>
       </c>
       <c r="Q9" s="15" t="s">
         <v>162</v>
@@ -2999,7 +2999,7 @@
         <v>220</v>
       </c>
       <c r="S9" s="16">
-        <v>0.147951919169033</v>
+        <v>0.1469082197446561</v>
       </c>
       <c r="T9" s="17" t="s">
         <v>162</v>
@@ -3008,7 +3008,7 @@
         <v>225</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1530008334433191</v>
+        <v>0.1532305271197326</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3020,7 +3020,7 @@
         <v>196</v>
       </c>
       <c r="D10" s="10">
-        <v>0.0768483539382471</v>
+        <v>0.0765556631134385</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>162</v>
@@ -3029,7 +3029,7 @@
         <v>201</v>
       </c>
       <c r="G10" s="12">
-        <v>0.04743474832835495</v>
+        <v>0.0473344129654589</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>166</v>
@@ -3038,7 +3038,7 @@
         <v>206</v>
       </c>
       <c r="J10" s="14">
-        <v>0.127047966127378</v>
+        <v>0.1258359093627484</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>166</v>
@@ -3047,7 +3047,7 @@
         <v>211</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1030468315152118</v>
+        <v>0.1037039171442513</v>
       </c>
       <c r="N10" s="17" t="s">
         <v>166</v>
@@ -3056,7 +3056,7 @@
         <v>216</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1283268681683046</v>
+        <v>0.1281983553287803</v>
       </c>
       <c r="Q10" s="15" t="s">
         <v>164</v>
@@ -3065,7 +3065,7 @@
         <v>221</v>
       </c>
       <c r="S10" s="16">
-        <v>0.09192674462386743</v>
+        <v>0.09346516709916426</v>
       </c>
       <c r="T10" s="17" t="s">
         <v>164</v>
@@ -3074,7 +3074,7 @@
         <v>226</v>
       </c>
       <c r="V10" s="18">
-        <v>0.08887855828736323</v>
+        <v>0.08886425190185546</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3086,7 +3086,7 @@
         <v>197</v>
       </c>
       <c r="D11" s="10">
-        <v>0.05901145088735264</v>
+        <v>0.05863844281434881</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>166</v>
@@ -3095,7 +3095,7 @@
         <v>202</v>
       </c>
       <c r="G11" s="12">
-        <v>0.03258239928739307</v>
+        <v>0.03314165687552613</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>172</v>
@@ -3104,7 +3104,7 @@
         <v>207</v>
       </c>
       <c r="J11" s="14">
-        <v>0.07864072771039093</v>
+        <v>0.0783525401685785</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>164</v>
@@ -3113,7 +3113,7 @@
         <v>212</v>
       </c>
       <c r="M11" s="16">
-        <v>0.09016438775662827</v>
+        <v>0.08971220399862974</v>
       </c>
       <c r="N11" s="17" t="s">
         <v>164</v>
@@ -3122,7 +3122,7 @@
         <v>217</v>
       </c>
       <c r="P11" s="18">
-        <v>0.06536307955168284</v>
+        <v>0.06570215053410727</v>
       </c>
       <c r="Q11" s="15" t="s">
         <v>166</v>
@@ -3131,7 +3131,7 @@
         <v>222</v>
       </c>
       <c r="S11" s="16">
-        <v>0.07299968931862934</v>
+        <v>0.0729738999065313</v>
       </c>
       <c r="T11" s="17" t="s">
         <v>166</v>
@@ -3140,7 +3140,7 @@
         <v>227</v>
       </c>
       <c r="V11" s="18">
-        <v>0.07922306118983646</v>
+        <v>0.07918900559572895</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3152,7 +3152,7 @@
         <v>198</v>
       </c>
       <c r="D12" s="10">
-        <v>0.05410882246704245</v>
+        <v>0.05399966796510131</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>168</v>
@@ -3161,7 +3161,7 @@
         <v>203</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01276420302501075</v>
+        <v>0.01274306703030801</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>164</v>
@@ -3170,7 +3170,7 @@
         <v>208</v>
       </c>
       <c r="J12" s="14">
-        <v>0.06369331334353838</v>
+        <v>0.06374403533730051</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>168</v>
@@ -3179,7 +3179,7 @@
         <v>213</v>
       </c>
       <c r="M12" s="16">
-        <v>0.03261584891771818</v>
+        <v>0.03263402128013062</v>
       </c>
       <c r="N12" s="17" t="s">
         <v>172</v>
@@ -3188,7 +3188,7 @@
         <v>218</v>
       </c>
       <c r="P12" s="18">
-        <v>0.03167782389386651</v>
+        <v>0.03178143715382588</v>
       </c>
       <c r="Q12" s="15" t="s">
         <v>168</v>
@@ -3197,7 +3197,7 @@
         <v>223</v>
       </c>
       <c r="S12" s="16">
-        <v>0.04444827038559346</v>
+        <v>0.04428043008863833</v>
       </c>
       <c r="T12" s="17" t="s">
         <v>168</v>
@@ -3206,7 +3206,7 @@
         <v>228</v>
       </c>
       <c r="V12" s="18">
-        <v>0.0446265053710589</v>
+        <v>0.04446900137787489</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3218,7 +3218,7 @@
         <v>199</v>
       </c>
       <c r="D13" s="10">
-        <v>0.05169289066119698</v>
+        <v>0.05282509661786941</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>172</v>
@@ -3227,7 +3227,7 @@
         <v>204</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01033351239919366</v>
+        <v>0.009838263666440908</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>170</v>
@@ -3236,7 +3236,7 @@
         <v>209</v>
       </c>
       <c r="J13" s="14">
-        <v>0.03790486816609744</v>
+        <v>0.03798236335169682</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>170</v>
@@ -3245,7 +3245,7 @@
         <v>214</v>
       </c>
       <c r="M13" s="16">
-        <v>0.02070781480229344</v>
+        <v>0.02005040245184064</v>
       </c>
       <c r="N13" s="17" t="s">
         <v>168</v>
@@ -3254,7 +3254,7 @@
         <v>219</v>
       </c>
       <c r="P13" s="18">
-        <v>0.03150130677897204</v>
+        <v>0.03151126909584334</v>
       </c>
       <c r="Q13" s="15" t="s">
         <v>170</v>
@@ -3263,7 +3263,7 @@
         <v>224</v>
       </c>
       <c r="S13" s="16">
-        <v>0.0301115159243705</v>
+        <v>0.02999781238246274</v>
       </c>
       <c r="T13" s="17" t="s">
         <v>172</v>
@@ -3272,7 +3272,7 @@
         <v>229</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02789153664290851</v>
+        <v>0.02796034021165866</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3352,7 +3352,7 @@
         <v>230</v>
       </c>
       <c r="D16" s="10">
-        <v>0.2306847864051237</v>
+        <v>0.2300114100649457</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>164</v>
@@ -3361,7 +3361,7 @@
         <v>235</v>
       </c>
       <c r="G16" s="12">
-        <v>0.3349782030249119</v>
+        <v>0.3346323671409909</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>162</v>
@@ -3370,7 +3370,7 @@
         <v>240</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1329696263311327</v>
+        <v>0.1335086413078485</v>
       </c>
       <c r="K16" s="15" t="s">
         <v>162</v>
@@ -3379,7 +3379,7 @@
         <v>245</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1463836130626502</v>
+        <v>0.1453540645238352</v>
       </c>
       <c r="N16" s="17" t="s">
         <v>162</v>
@@ -3388,7 +3388,7 @@
         <v>250</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1590318400911928</v>
+        <v>0.1584214801470401</v>
       </c>
       <c r="Q16" s="15" t="s">
         <v>162</v>
@@ -3397,7 +3397,7 @@
         <v>255</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1767259624467802</v>
+        <v>0.1762343743106544</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>162</v>
@@ -3406,7 +3406,7 @@
         <v>260</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1440263073697532</v>
+        <v>0.1433320900157327</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3418,7 +3418,7 @@
         <v>231</v>
       </c>
       <c r="D17" s="10">
-        <v>0.07893970720840247</v>
+        <v>0.07934538791056667</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>162</v>
@@ -3427,7 +3427,7 @@
         <v>236</v>
       </c>
       <c r="G17" s="12">
-        <v>0.05147385745016131</v>
+        <v>0.05131193841868747</v>
       </c>
       <c r="H17" s="13" t="s">
         <v>164</v>
@@ -3436,7 +3436,7 @@
         <v>241</v>
       </c>
       <c r="J17" s="14">
-        <v>0.09060959604448168</v>
+        <v>0.09045862216373554</v>
       </c>
       <c r="K17" s="15" t="s">
         <v>164</v>
@@ -3445,7 +3445,7 @@
         <v>246</v>
       </c>
       <c r="M17" s="16">
-        <v>0.09814896880369718</v>
+        <v>0.09951335943234946</v>
       </c>
       <c r="N17" s="17" t="s">
         <v>166</v>
@@ -3454,7 +3454,7 @@
         <v>251</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1247122215990866</v>
+        <v>0.1249190268452674</v>
       </c>
       <c r="Q17" s="15" t="s">
         <v>164</v>
@@ -3463,7 +3463,7 @@
         <v>256</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1476184793727428</v>
+        <v>0.1491999587441493</v>
       </c>
       <c r="T17" s="17" t="s">
         <v>164</v>
@@ -3472,7 +3472,7 @@
         <v>261</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1318315043034123</v>
+        <v>0.1324156456196653</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -3484,7 +3484,7 @@
         <v>232</v>
       </c>
       <c r="D18" s="10">
-        <v>0.05380131643013759</v>
+        <v>0.05365625441649019</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>166</v>
@@ -3493,7 +3493,7 @@
         <v>237</v>
       </c>
       <c r="G18" s="12">
-        <v>0.03855895085550629</v>
+        <v>0.03813229264445069</v>
       </c>
       <c r="H18" s="13" t="s">
         <v>166</v>
@@ -3502,7 +3502,7 @@
         <v>242</v>
       </c>
       <c r="J18" s="14">
-        <v>0.08546850653606095</v>
+        <v>0.08723218647975106</v>
       </c>
       <c r="K18" s="15" t="s">
         <v>166</v>
@@ -3511,7 +3511,7 @@
         <v>247</v>
       </c>
       <c r="M18" s="16">
-        <v>0.08831626245414781</v>
+        <v>0.08785332136093897</v>
       </c>
       <c r="N18" s="17" t="s">
         <v>164</v>
@@ -3520,7 +3520,7 @@
         <v>252</v>
       </c>
       <c r="P18" s="18">
-        <v>0.09198025150344154</v>
+        <v>0.09089435746097538</v>
       </c>
       <c r="Q18" s="15" t="s">
         <v>166</v>
@@ -3529,7 +3529,7 @@
         <v>257</v>
       </c>
       <c r="S18" s="16">
-        <v>0.097776497766686</v>
+        <v>0.09731955007769733</v>
       </c>
       <c r="T18" s="17" t="s">
         <v>166</v>
@@ -3538,7 +3538,7 @@
         <v>262</v>
       </c>
       <c r="V18" s="18">
-        <v>0.1033640294445006</v>
+        <v>0.1028968300617401</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -3550,7 +3550,7 @@
         <v>233</v>
       </c>
       <c r="D19" s="10">
-        <v>0.04370863845407737</v>
+        <v>0.0435952364844587</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>168</v>
@@ -3559,7 +3559,7 @@
         <v>238</v>
       </c>
       <c r="G19" s="12">
-        <v>0.02702619621724013</v>
+        <v>0.02698144406632531</v>
       </c>
       <c r="H19" s="13" t="s">
         <v>168</v>
@@ -3568,7 +3568,7 @@
         <v>243</v>
       </c>
       <c r="J19" s="14">
-        <v>0.05546907774733206</v>
+        <v>0.05605556153623258</v>
       </c>
       <c r="K19" s="15" t="s">
         <v>170</v>
@@ -3577,7 +3577,7 @@
         <v>248</v>
       </c>
       <c r="M19" s="16">
-        <v>0.05172329374649121</v>
+        <v>0.05189401006150508</v>
       </c>
       <c r="N19" s="17" t="s">
         <v>168</v>
@@ -3586,7 +3586,7 @@
         <v>253</v>
       </c>
       <c r="P19" s="18">
-        <v>0.071358284936927</v>
+        <v>0.07199184979795661</v>
       </c>
       <c r="Q19" s="15" t="s">
         <v>168</v>
@@ -3595,7 +3595,7 @@
         <v>258</v>
       </c>
       <c r="S19" s="16">
-        <v>0.05585921661504464</v>
+        <v>0.05602812612432077</v>
       </c>
       <c r="T19" s="17" t="s">
         <v>168</v>
@@ -3604,7 +3604,7 @@
         <v>263</v>
       </c>
       <c r="V19" s="18">
-        <v>0.04968944238616621</v>
+        <v>0.04974086057865899</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -3616,7 +3616,7 @@
         <v>234</v>
       </c>
       <c r="D20" s="10">
-        <v>0.02519776051710931</v>
+        <v>0.02497210377104306</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>172</v>
@@ -3625,7 +3625,7 @@
         <v>239</v>
       </c>
       <c r="G20" s="12">
-        <v>0.00844386431731459</v>
+        <v>0.008429882287168899</v>
       </c>
       <c r="H20" s="13" t="s">
         <v>170</v>
@@ -3634,7 +3634,7 @@
         <v>244</v>
       </c>
       <c r="J20" s="14">
-        <v>0.03285856495933279</v>
+        <v>0.03134716940647311</v>
       </c>
       <c r="K20" s="15" t="s">
         <v>168</v>
@@ -3643,7 +3643,7 @@
         <v>249</v>
       </c>
       <c r="M20" s="16">
-        <v>0.04600160376181367</v>
+        <v>0.04586807760945783</v>
       </c>
       <c r="N20" s="17" t="s">
         <v>170</v>
@@ -3652,7 +3652,7 @@
         <v>254</v>
       </c>
       <c r="P20" s="18">
-        <v>0.02551591220162323</v>
+        <v>0.0259914026930745</v>
       </c>
       <c r="Q20" s="15" t="s">
         <v>170</v>
@@ -3661,7 +3661,7 @@
         <v>259</v>
       </c>
       <c r="S20" s="16">
-        <v>0.03151597632789479</v>
+        <v>0.03128994876743985</v>
       </c>
       <c r="T20" s="17" t="s">
         <v>172</v>
@@ -3670,7 +3670,7 @@
         <v>264</v>
       </c>
       <c r="V20" s="18">
-        <v>0.03070251352538597</v>
+        <v>0.03073428421297372</v>
       </c>
     </row>
   </sheetData>
